--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125725650</v>
       </c>
       <c r="B3" t="n">
-        <v>100922</v>
+        <v>100929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125724354</v>
       </c>
       <c r="B4" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125735702</v>
       </c>
       <c r="B5" t="n">
-        <v>105260</v>
+        <v>105267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100922</v>
+        <v>100929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100929</v>
+        <v>100930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125725650</v>
       </c>
       <c r="B3" t="n">
-        <v>100929</v>
+        <v>100932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125724354</v>
       </c>
       <c r="B4" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125735702</v>
       </c>
       <c r="B5" t="n">
-        <v>105267</v>
+        <v>105270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100930</v>
+        <v>100932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125725650</v>
       </c>
       <c r="B3" t="n">
-        <v>100932</v>
+        <v>100936</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125724354</v>
       </c>
       <c r="B4" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125735702</v>
       </c>
       <c r="B5" t="n">
-        <v>105270</v>
+        <v>105274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100932</v>
+        <v>100936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125725650</v>
       </c>
       <c r="B3" t="n">
-        <v>100936</v>
+        <v>100937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125724354</v>
       </c>
       <c r="B4" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125735702</v>
       </c>
       <c r="B5" t="n">
-        <v>105274</v>
+        <v>105275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100936</v>
+        <v>100937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125725650</v>
       </c>
       <c r="B3" t="n">
-        <v>100937</v>
+        <v>100939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125724354</v>
       </c>
       <c r="B4" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125735702</v>
       </c>
       <c r="B5" t="n">
-        <v>105275</v>
+        <v>105277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100937</v>
+        <v>100939</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125725650</v>
       </c>
       <c r="B3" t="n">
-        <v>100939</v>
+        <v>100941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125724354</v>
       </c>
       <c r="B4" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125735702</v>
       </c>
       <c r="B5" t="n">
-        <v>105277</v>
+        <v>105279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100939</v>
+        <v>100941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125725650</v>
       </c>
       <c r="B3" t="n">
-        <v>100941</v>
+        <v>100943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125724354</v>
       </c>
       <c r="B4" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125735702</v>
       </c>
       <c r="B5" t="n">
-        <v>105279</v>
+        <v>105283</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100941</v>
+        <v>100943</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125725650</v>
       </c>
       <c r="B3" t="n">
-        <v>100943</v>
+        <v>100947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125724354</v>
       </c>
       <c r="B4" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125735702</v>
       </c>
       <c r="B5" t="n">
-        <v>105283</v>
+        <v>105296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100943</v>
+        <v>100947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125725650</v>
       </c>
       <c r="B3" t="n">
-        <v>100947</v>
+        <v>100950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125724354</v>
       </c>
       <c r="B4" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125735702</v>
       </c>
       <c r="B5" t="n">
-        <v>105296</v>
+        <v>105299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100947</v>
+        <v>100950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32879-2019 artfynd.xlsx
+++ b/artfynd/A 32879-2019 artfynd.xlsx
@@ -1378,7 +1378,7 @@
         <v>125855273</v>
       </c>
       <c r="B8" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>125873159</v>
       </c>
       <c r="B9" t="n">
-        <v>100950</v>
+        <v>100959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
